--- a/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/log_excepciones.xlsx
+++ b/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/log_excepciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>tipo_alerta</t>
   </si>
@@ -40,15 +40,6 @@
     <t>banca_corporativa.xlsx</t>
   </si>
   <si>
-    <t>cumplimiento.xlsx</t>
-  </si>
-  <si>
-    <t>proveedor_servicios.xlsx</t>
-  </si>
-  <si>
-    <t>proveedor_ti.xlsx</t>
-  </si>
-  <si>
     <t>seguros.xlsx</t>
   </si>
   <si>
@@ -61,30 +52,9 @@
     <t>banca_comercial.xlsx</t>
   </si>
   <si>
-    <t>riesgos.xlsx</t>
-  </si>
-  <si>
     <t>Spread financiero</t>
   </si>
   <si>
-    <t>Multas regulatorias</t>
-  </si>
-  <si>
-    <t>Renta de inmuebles</t>
-  </si>
-  <si>
-    <t>Mantenimiento y limpieza</t>
-  </si>
-  <si>
-    <t>Servicios de seguridad</t>
-  </si>
-  <si>
-    <t>Licencias de software</t>
-  </si>
-  <si>
-    <t>Servicios de TI externos</t>
-  </si>
-  <si>
     <t>Reserva técnica seguros</t>
   </si>
   <si>
@@ -106,25 +76,22 @@
     <t>Registro con monto vacío o NaN</t>
   </si>
   <si>
-    <t>Monto 9,149,128.84 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 13,108,478.78 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 16,822,601.53 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 9,787,663.59 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 16,809,829.15 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 14,949,989.11 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
-  </si>
-  <si>
-    <t>Monto 14,180,711.93 excede 3 desviaciones estándar (media=2,602,329.25, std=1,797,438.51)</t>
+    <t>Monto 9,149,128.84 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
+  </si>
+  <si>
+    <t>Monto 13,108,478.78 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
+  </si>
+  <si>
+    <t>Monto 9,787,663.59 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
+  </si>
+  <si>
+    <t>Monto 16,809,829.15 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
+  </si>
+  <si>
+    <t>Monto 14,949,989.11 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
+  </si>
+  <si>
+    <t>Monto 14,180,711.93 excede 3 desviaciones estándar (media=2,549,263.70, std=1,840,950.36)</t>
   </si>
 </sst>
 </file>
@@ -456,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -484,10 +451,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -498,10 +465,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -512,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -523,258 +490,115 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>9149128.84</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>13108478.78</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>9787663.59</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>16809829.15</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>14949989.11</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>14180711.93</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
         <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15">
-        <v>9149128.84</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16">
-        <v>13108478.78</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17">
-        <v>16822601.53</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18">
-        <v>9787663.59</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19">
-        <v>16809829.15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20">
-        <v>14949989.11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21">
-        <v>14180711.93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
